--- a/experimentos/resultados/exp_prefiltro_max_mecanismo.xlsx
+++ b/experimentos/resultados/exp_prefiltro_max_mecanismo.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen_top10" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sacados_del_top10" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="juzgados_enmascarados" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="positivos_GA_enmascarados" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choco_GA_top10" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enmascarados_por_ambito" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen_top10" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sacados_del_top10" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="juzgados_enmascarados" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="positivos_GA_enmascarados" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choco_GA_top10" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,59 +430,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>umbral</t>
+          <t>ambito</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>celdas</t>
+          <t>articulos</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>puestos_top10</t>
+          <t>enmascarados</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>articulos_sacados</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>sacados_positivos</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>sacados_no_positivos</t>
+          <t>pct_enmascarado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0.85</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>nacional (32 departamentos)</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>11439</v>
       </c>
       <c r="C2" t="n">
-        <v>225</v>
+        <v>1442</v>
       </c>
       <c r="D2" t="n">
-        <v>27</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26</v>
+        <v>0.1260599702771221</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Antioquia (2023)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>494</v>
+      </c>
+      <c r="C3" t="n">
+        <v>65</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.131578947368421</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Municipio Maicao</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1101</v>
+      </c>
+      <c r="C4" t="n">
+        <v>113</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1026339691189827</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Municipio Oicatá</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.40625</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Vereda Paraguachón</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -495,827 +546,99 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>indicador</t>
+          <t>umbral</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>lugar</t>
+          <t>celdas</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>rango_sin_mascara</t>
+          <t>puestos_top10</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>articulos_sacados</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>score_social</t>
+          <t>sacados_positivos</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>positivo_de_referencia</t>
+          <t>sacados_no_positivos</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>titulo</t>
+          <t>puestos_positivos</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>puestos_no_positivos</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>no_positivos_que_pasan</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>pct_no_positivos_que_pasan</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>mediana_social_de_los_que_pasan</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>exclusion_beneficios_economicos</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Maicao</t>
-        </is>
+      <c r="A2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="B2" t="n">
+        <v>23</v>
       </c>
       <c r="C2" t="n">
+        <v>225</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.9960558939566545</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.1587677001953125</v>
-      </c>
-      <c r="F2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Unidad de Búsqueda recupera 25 cuerpos en cementerio de Riohacha</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>exclusion_beneficios_economicos</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Maicao</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.9938835407030947</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.6979589462280273</v>
-      </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Paraguachón, frontera cerrada: así se vive en La Guajira el bloqueo del paso entre Colombia y Venezuela tras la captura de Nicolás Maduro</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>exclusion_beneficios_economicos</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Maicao</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.9916310566706535</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.4525233805179596</v>
-      </c>
-      <c r="F4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Operativos de control dejan dos capturados por presunto tráfico de estupefacientes en Riohacha y Maicao</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>desplazamiento_forzado</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Maicao</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.9830825904627406</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.1805854141712189</v>
-      </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Ofrecen hasta $100 millones para lograr liberación de Angie Argáez</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>presencia_grupos_armados</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Maicao</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.9750501191116061</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.8311508893966675</v>
-      </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Refuerzan en Maicao la estrategia ‘Turismo Seguro’ con acciones preventivas en zonas de alta afluencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>exclusion_beneficios_economicos</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Oicata</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.9887204645183667</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.5673011541366577</v>
-      </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>La Unidad de Búsqueda de Personas recuperó diez cuerpos en el cementerio de Oicatá</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>exclusion_beneficios_economicos</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Oicata</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.95803142989861</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.1855590641498566</v>
-      </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Estos fueron los compromisos acordados tras las protestas en el peaje de Tuta</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>exclusion_beneficios_economicos</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Oicata</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.8045822040993865</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.4809575080871582</v>
-      </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Así fue la cadena de fallas que llevó al choque mortal del camión de gas en la vía Simijaca - Chiquinquirá, Cundinamarca: 'La tragedia pudo ser peor'</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>exclusion_beneficios_economicos</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Oicata</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>7</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.7467726683511684</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.03317741677165031</v>
-      </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Duitama fue escenario del reencuentro regional de madres comunitarias tras más de diez años</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>rechazo_proyecto</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Oicata</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.9792000326800691</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.1855590641498566</v>
-      </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Estos fueron los compromisos acordados tras las protestas en el peaje de Tuta</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>rechazo_proyecto</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Oicata</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.6931706727192185</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.8181499242782593</v>
-      </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Nueva encuesta Guarumo: así ha sido la intención de voto de Paloma Valencia, pasó de 6,9 por ciento en enero a 19,9 por ciento en marzo</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>rechazo_proyecto</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Oicata</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>6</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.6337039165660141</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.7807539701461792</v>
-      </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Familia y bomberos exigen a Fiscalía recapturar al tatuador señalado de agredir al comandante Jairo Bolívar: sigue en UCI tras brutal golpiza en Tunja</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>rechazo_proyecto</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Oicata</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>9</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.5645777327712558</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.4525963366031647</v>
-      </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>¿Por qué Cepeda lidera la intención de voto, De la Espriella se sostiene y Valencia crece? Análisis de la encuesta de Guarumo y Ecoanalítica</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>desplazamiento_forzado</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Oicata</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.5169579832509097</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.8181499242782593</v>
-      </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Nueva encuesta Guarumo: así ha sido la intención de voto de Paloma Valencia, pasó de 6,9 por ciento en enero a 19,9 por ciento en marzo</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>desplazamiento_forzado</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Oicata</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>7</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.00751888297412262</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.1855590641498566</v>
-      </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Estos fueron los compromisos acordados tras las protestas en el peaje de Tuta</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>conflicto_territorial</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Oicata</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.6715507987765823</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.8181499242782593</v>
-      </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Nueva encuesta Guarumo: así ha sido la intención de voto de Paloma Valencia, pasó de 6,9 por ciento en enero a 19,9 por ciento en marzo</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>conflicto_territorial</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Oicata</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.3836431503875382</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.7807539701461792</v>
-      </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Familia y bomberos exigen a Fiscalía recapturar al tatuador señalado de agredir al comandante Jairo Bolívar: sigue en UCI tras brutal golpiza en Tunja</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>presencia_grupos_armados</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Oicata</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.3491775515019979</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.7807539701461792</v>
-      </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Familia y bomberos exigen a Fiscalía recapturar al tatuador señalado de agredir al comandante Jairo Bolívar: sigue en UCI tras brutal golpiza en Tunja</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>presencia_grupos_armados</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Oicata</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>7</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4.068590082895174e-06</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.5673011541366577</v>
-      </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>La Unidad de Búsqueda de Personas recuperó diez cuerpos en el cementerio de Oicatá</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>exclusion_beneficios_economicos</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Paraguachon</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.9938835407030947</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.6979589462280273</v>
-      </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Paraguachón, frontera cerrada: así se vive en La Guajira el bloqueo del paso entre Colombia y Venezuela tras la captura de Nicolás Maduro</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>exclusion_beneficios_economicos</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Paraguachon</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>6</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.9679911120110569</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.2754774987697601</v>
-      </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Presidente Macron confirma la liberación de Camilo Castro, francés detenido en Venezuela desde junio, y anuncia que ya viaja hacia Francia</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>exclusion_beneficios_economicos</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Paraguachon</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>10</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.9121253921002337</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.7836817502975464</v>
-      </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Operativos en La Guajira dejan seis capturados y recuperación de tres motocicletas hurtadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>rechazo_proyecto</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Paraguachon</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>4</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.93333789324408</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.2754774987697601</v>
-      </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Presidente Macron confirma la liberación de Camilo Castro, francés detenido en Venezuela desde junio, y anuncia que ya viaja hacia Francia</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>conflicto_territorial</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Paraguachon</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>10</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.7115685959518868</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.407474011182785</v>
-      </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>La Guajira | Normalidad en la frontera tras reapertura del paso en Paraguachón por parte de las autoridades venezolanas: Maicao se mantiene en alerta</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>presencia_grupos_armados</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Paraguachon</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.9142890937817995</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.7836817502975464</v>
-      </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Operativos en La Guajira dejan seis capturados y recuperación de tres motocicletas hurtadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>presencia_grupos_armados</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Chocó</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.9904675440133539</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.04873302578926086</v>
-      </c>
-      <c r="F27" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Chocó: 79% de los confinamientos y el segundo con más desplazamientos</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>presencia_grupos_armados</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>2</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.9766778759892673</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.7348201870918274</v>
-      </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Dos ejemplos de elegir bien</t>
-        </is>
+      <c r="F2" t="n">
+        <v>26</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H2" t="n">
+        <v>199</v>
+      </c>
+      <c r="I2" t="n">
+        <v>173</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8693467336683417</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.9975117444992065</v>
       </c>
     </row>
   </sheetData>
@@ -1329,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1340,32 +663,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>positivos</t>
+          <t>lugar</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>positivos_enmascarados</t>
+          <t>rango_sin_mascara</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>frac_positivos_enmascarados</t>
+          <t>score</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>negativos</t>
+          <t>score_social</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>negativos_enmascarados</t>
+          <t>positivo_de_referencia</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>frac_negativos_enmascarados</t>
+          <t>titulo</t>
         </is>
       </c>
     </row>
@@ -1375,98 +698,114 @@
           <t>exclusion_beneficios_economicos</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Maicao</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.9960558939566545</v>
       </c>
       <c r="E2" t="n">
-        <v>759</v>
-      </c>
-      <c r="F2" t="n">
-        <v>88</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.1159420289855072</v>
+        <v>0.1587677001953125</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Unidad de Búsqueda recupera 25 cuerpos en cementerio de Riohacha</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rechazo_proyecto</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>8</v>
+          <t>exclusion_beneficios_economicos</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Maicao</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.9938835407030947</v>
       </c>
       <c r="E3" t="n">
-        <v>751</v>
-      </c>
-      <c r="F3" t="n">
-        <v>88</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.1171770972037284</v>
+        <v>0.6979589462280273</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Paraguachón, frontera cerrada: así se vive en La Guajira el bloqueo del paso entre Colombia y Venezuela tras la captura de Nicolás Maduro</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>desplazamiento_forzado</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>29</v>
+          <t>exclusion_beneficios_economicos</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Maicao</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.9916310566706535</v>
       </c>
       <c r="E4" t="n">
-        <v>730</v>
-      </c>
-      <c r="F4" t="n">
-        <v>88</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.1205479452054795</v>
+        <v>0.4525233805179596</v>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Operativos de control dejan dos capturados por presunto tráfico de estupefacientes en Riohacha y Maicao</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>conflicto_territorial</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>34</v>
+          <t>desplazamiento_forzado</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Maicao</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.9830825904627406</v>
       </c>
       <c r="E5" t="n">
-        <v>725</v>
-      </c>
-      <c r="F5" t="n">
-        <v>88</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.1213793103448276</v>
+        <v>0.1805854141712189</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ofrecen hasta $100 millones para lograr liberación de Angie Argáez</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1475,23 +814,665 @@
           <t>presencia_grupos_armados</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>128</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Maicao</t>
+        </is>
       </c>
       <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9750501191116061</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8311508893966675</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Refuerzan en Maicao la estrategia ‘Turismo Seguro’ con acciones preventivas en zonas de alta afluencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>exclusion_beneficios_economicos</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Oicata</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9887204645183667</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5673011541366577</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>La Unidad de Búsqueda de Personas recuperó diez cuerpos en el cementerio de Oicatá</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>exclusion_beneficios_economicos</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Oicata</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.95803142989861</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1855590641498566</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Estos fueron los compromisos acordados tras las protestas en el peaje de Tuta</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>exclusion_beneficios_economicos</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Oicata</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.0390625</v>
-      </c>
-      <c r="E6" t="n">
-        <v>631</v>
-      </c>
-      <c r="F6" t="n">
-        <v>83</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.1315372424722663</v>
+      <c r="D9" t="n">
+        <v>0.8045822040993865</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.4809575080871582</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Así fue la cadena de fallas que llevó al choque mortal del camión de gas en la vía Simijaca - Chiquinquirá, Cundinamarca: 'La tragedia pudo ser peor'</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>exclusion_beneficios_economicos</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Oicata</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.7467726683511684</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.03317741677165031</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Duitama fue escenario del reencuentro regional de madres comunitarias tras más de diez años</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>rechazo_proyecto</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Oicata</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.9792000326800691</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1855590641498566</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Estos fueron los compromisos acordados tras las protestas en el peaje de Tuta</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>rechazo_proyecto</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Oicata</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.6931706727192185</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.8181499242782593</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nueva encuesta Guarumo: así ha sido la intención de voto de Paloma Valencia, pasó de 6,9 por ciento en enero a 19,9 por ciento en marzo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>rechazo_proyecto</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Oicata</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.6337039165660141</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7807539701461792</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Familia y bomberos exigen a Fiscalía recapturar al tatuador señalado de agredir al comandante Jairo Bolívar: sigue en UCI tras brutal golpiza en Tunja</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>rechazo_proyecto</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Oicata</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.5645777327712558</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.4525963366031647</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>¿Por qué Cepeda lidera la intención de voto, De la Espriella se sostiene y Valencia crece? Análisis de la encuesta de Guarumo y Ecoanalítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>desplazamiento_forzado</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Oicata</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5169579832509097</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8181499242782593</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nueva encuesta Guarumo: así ha sido la intención de voto de Paloma Valencia, pasó de 6,9 por ciento en enero a 19,9 por ciento en marzo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>desplazamiento_forzado</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Oicata</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.00751888297412262</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.1855590641498566</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Estos fueron los compromisos acordados tras las protestas en el peaje de Tuta</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>conflicto_territorial</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Oicata</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.6715507987765823</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8181499242782593</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nueva encuesta Guarumo: así ha sido la intención de voto de Paloma Valencia, pasó de 6,9 por ciento en enero a 19,9 por ciento en marzo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>conflicto_territorial</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Oicata</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.3836431503875382</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7807539701461792</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Familia y bomberos exigen a Fiscalía recapturar al tatuador señalado de agredir al comandante Jairo Bolívar: sigue en UCI tras brutal golpiza en Tunja</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>presencia_grupos_armados</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Oicata</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.3491775515019979</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7807539701461792</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Familia y bomberos exigen a Fiscalía recapturar al tatuador señalado de agredir al comandante Jairo Bolívar: sigue en UCI tras brutal golpiza en Tunja</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>presencia_grupos_armados</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Oicata</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>7</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.068590082895174e-06</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.5673011541366577</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>La Unidad de Búsqueda de Personas recuperó diez cuerpos en el cementerio de Oicatá</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>exclusion_beneficios_economicos</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Paraguachon</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.9938835407030947</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.6979589462280273</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Paraguachón, frontera cerrada: así se vive en La Guajira el bloqueo del paso entre Colombia y Venezuela tras la captura de Nicolás Maduro</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>exclusion_beneficios_economicos</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Paraguachon</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.9679911120110569</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.2754774987697601</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Presidente Macron confirma la liberación de Camilo Castro, francés detenido en Venezuela desde junio, y anuncia que ya viaja hacia Francia</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exclusion_beneficios_economicos</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Paraguachon</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.9121253921002337</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.7836817502975464</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Operativos en La Guajira dejan seis capturados y recuperación de tres motocicletas hurtadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>rechazo_proyecto</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Paraguachon</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.93333789324408</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.2754774987697601</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Presidente Macron confirma la liberación de Camilo Castro, francés detenido en Venezuela desde junio, y anuncia que ya viaja hacia Francia</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>conflicto_territorial</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Paraguachon</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.7115685959518868</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.407474011182785</v>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>La Guajira | Normalidad en la frontera tras reapertura del paso en Paraguachón por parte de las autoridades venezolanas: Maicao se mantiene en alerta</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>presencia_grupos_armados</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Paraguachon</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.9142890937817995</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7836817502975464</v>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Operativos en La Guajira dejan seis capturados y recuperación de tres motocicletas hurtadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>presencia_grupos_armados</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Chocó</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.9904675440133539</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.04873302578926086</v>
+      </c>
+      <c r="F27" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Chocó: 79% de los confinamientos y el segundo con más desplazamientos</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>presencia_grupos_armados</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.9766778759892673</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7348201870918274</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dos ejemplos de elegir bien</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1505,139 +1486,169 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>lugar</t>
+          <t>indicador</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>rango_sin_mascara</t>
+          <t>positivos</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>positivos_enmascarados</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>score_social</t>
+          <t>frac_positivos_enmascarados</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>titulo</t>
+          <t>negativos</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>negativos_enmascarados</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>frac_negativos_enmascarados</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Maicao</t>
+          <t>exclusion_beneficios_economicos</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8631166998286253</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8272041082382202</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Ejército y Policía refuerzan ofensiva contra Los Pachenca y bandas criminales en La Guajira</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>759</v>
+      </c>
+      <c r="F2" t="n">
+        <v>88</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1159420289855072</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Maicao</t>
+          <t>rechazo_proyecto</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8220845744057692</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8033056259155273</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Capturan presuntos integrantes de estructura criminal en La Guajira</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>751</v>
+      </c>
+      <c r="F3" t="n">
+        <v>88</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1171770972037284</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Maicao</t>
+          <t>desplazamiento_forzado</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9554615897683564</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6525524258613586</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>El bloqueo en la Troncal del Caribe con el que se buscó evitar el traslado de la 'Bebecita', compañera sentimental de cabecilla de ‘los Pachencas’</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>730</v>
+      </c>
+      <c r="F4" t="n">
+        <v>88</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1205479452054795</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chocó</t>
+          <t>conflicto_territorial</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9904675440133539</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04873302578926086</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Chocó: 79% de los confinamientos y el segundo con más desplazamientos</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>725</v>
+      </c>
+      <c r="F5" t="n">
+        <v>88</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1213793103448276</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>presencia_grupos_armados</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>128</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8850083729614254</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5979536175727844</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Empieza la toma oficial de la región del Sumapaz</t>
-        </is>
+        <v>0.0390625</v>
+      </c>
+      <c r="E6" t="n">
+        <v>631</v>
+      </c>
+      <c r="F6" t="n">
+        <v>83</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1315372424722663</v>
       </c>
     </row>
   </sheetData>
@@ -1651,6 +1662,152 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>lugar</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>rango_sin_mascara</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>score_social</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>titulo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Maicao</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.8631166998286253</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8272041082382202</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Ejército y Policía refuerzan ofensiva contra Los Pachenca y bandas criminales en La Guajira</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Maicao</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>64</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8220845744057692</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8033056259155273</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Capturan presuntos integrantes de estructura criminal en La Guajira</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Maicao</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9554615897683564</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.6525524258613586</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>El bloqueo en la Troncal del Caribe con el que se buscó evitar el traslado de la 'Bebecita', compañera sentimental de cabecilla de ‘los Pachencas’</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chocó</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9904675440133539</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.04873302578926086</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Chocó: 79% de los confinamientos y el segundo con más desplazamientos</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8850083729614254</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5979536175727844</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Empieza la toma oficial de la región del Sumapaz</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
